--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11422,12 +11422,12 @@
       <c r="P184" s="1" t="inlineStr"/>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11422,12 +11422,12 @@
       <c r="P184" s="1" t="inlineStr"/>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11422,12 +11422,12 @@
       <c r="P184" s="1" t="inlineStr"/>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -11427,7 +11427,7 @@
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Milano_2027.xlsx
+++ b/Verifica_Milano_2027.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -11384,50 +11377,39 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="inlineStr">
+      <c r="A184" t="inlineStr">
         <is>
           <t>Barba</t>
         </is>
       </c>
-      <c r="B184" s="1" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Via San Gregorio, 40</t>
         </is>
       </c>
-      <c r="C184" s="1" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>02/36515846</t>
         </is>
       </c>
-      <c r="D184" s="1" t="inlineStr"/>
-      <c r="E184" s="1" t="inlineStr"/>
-      <c r="F184" s="1" t="inlineStr"/>
-      <c r="G184" s="1" t="inlineStr"/>
-      <c r="H184" s="1" t="inlineStr"/>
-      <c r="I184" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J184" s="1" t="inlineStr">
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="K184" s="1" t="inlineStr"/>
-      <c r="L184" s="1" t="inlineStr"/>
-      <c r="M184" s="1" t="inlineStr"/>
-      <c r="N184" s="1" t="inlineStr"/>
-      <c r="O184" s="1" t="inlineStr"/>
-      <c r="P184" s="1" t="inlineStr"/>
-      <c r="Q184" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R184" s="1" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
